--- a/presentation/Παρουσίαση εργασίας 2.xlsx
+++ b/presentation/Παρουσίαση εργασίας 2.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yiann\OneDrive\Υπολογιστής\Σχολείο\ΟΠΑ\Δομές δεδομένων\Εργασία 2\presentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD4EF2F-E940-489F-9AA7-1C83E0E62753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7AEDF6-A4C7-482A-8E3C-8A3C9A1C166D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Φύλλο1" sheetId="1" r:id="rId1"/>
+    <sheet name="Linear data" sheetId="1" r:id="rId1"/>
+    <sheet name="Logarithmic data" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
   <si>
     <t>Number of Folders</t>
   </si>
@@ -50,7 +51,7 @@
     <t>Precentile difference</t>
   </si>
   <si>
-    <t>Difference</t>
+    <t>Difference from greedy to greedy decreasing algorithm</t>
   </si>
 </sst>
 </file>
@@ -200,7 +201,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Φύλλο1!$A$2</c:f>
+              <c:f>'Linear data'!$A$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -281,7 +282,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Φύλλο1!$B$1:$K$1</c:f>
+              <c:f>'Linear data'!$B$1:$K$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -320,7 +321,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Φύλλο1!$B$2:$K$2</c:f>
+              <c:f>'Linear data'!$B$2:$K$2</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -369,7 +370,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Φύλλο1!$A$3</c:f>
+              <c:f>'Linear data'!$A$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -538,7 +539,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Φύλλο1!$B$1:$K$1</c:f>
+              <c:f>'Linear data'!$B$1:$K$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -577,7 +578,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Φύλλο1!$B$3:$K$3</c:f>
+              <c:f>'Linear data'!$B$3:$K$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -1028,7 +1029,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Φύλλο1!$B$1:$K$1</c:f>
+              <c:f>'Linear data'!$B$1:$K$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -1067,39 +1068,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Φύλλο1!$B$4:$K$4</c:f>
+              <c:f>'Linear data'!$B$4:$K$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>6.1999999999999957</c:v>
+                  <c:v>-6.1999999999999957</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21.699999999999989</c:v>
+                  <c:v>-21.699999999999989</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>36.800000000000011</c:v>
+                  <c:v>-36.800000000000011</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>53.5</c:v>
+                  <c:v>-53.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>68.700000000000045</c:v>
+                  <c:v>-68.700000000000045</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>85.699999999999932</c:v>
+                  <c:v>-85.699999999999932</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>102</c:v>
+                  <c:v>-102</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>116.34999999999991</c:v>
+                  <c:v>-116.34999999999991</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>134.25</c:v>
+                  <c:v>-134.25</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>152.5</c:v>
+                  <c:v>-152.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1484,7 +1485,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Φύλλο1!$B$1:$K$1</c:f>
+              <c:f>'Linear data'!$B$1:$K$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -1523,39 +1524,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Φύλλο1!$B$5:$K$5</c:f>
+              <c:f>'Linear data'!$B$5:$K$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>12</c:v>
+                  <c:v>-11</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14.000000000000002</c:v>
+                  <c:v>-12</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.000000000000002</c:v>
+                  <c:v>-13</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15</c:v>
+                  <c:v>-13</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15</c:v>
+                  <c:v>-13</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>15</c:v>
+                  <c:v>-13</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>15</c:v>
+                  <c:v>-13</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>15</c:v>
+                  <c:v>-13</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>16</c:v>
+                  <c:v>-13</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>16</c:v>
+                  <c:v>-14.000000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1564,6 +1565,1743 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-9DE0-487C-9535-C707D4CC9049}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1485362208"/>
+        <c:axId val="1485362624"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1485362208"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Number of folders</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1485362624"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1485362624"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>% difference</a:t>
+                </a:r>
+                <a:endParaRPr lang="el-GR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1485362208"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="el-GR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Disks</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> used by algorithm</a:t>
+            </a:r>
+            <a:endParaRPr lang="el-GR"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.4885529819721436E-2"/>
+          <c:y val="0.11557971014492753"/>
+          <c:w val="0.90425941282887079"/>
+          <c:h val="0.66086161676808042"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Logarithmic data'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Greedy Algorithm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Logarithmic data'!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1900</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Logarithmic data'!$B$2:$K$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>58.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>177.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>293.75</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>411.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>528.45000000000005</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>646.29999999999995</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>762.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>881.3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>995.55</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1105.3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0FF1-4E74-A1A5-9B44EC70D1EA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Logarithmic data'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Greedy Decreasing Algorithm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="4.4618217468100365E-4"/>
+                  <c:y val="1.4593246242070085E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-0FF1-4E74-A1A5-9B44EC70D1EA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.3116602957219044E-2"/>
+                  <c:y val="2.4305931748627423E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-0FF1-4E74-A1A5-9B44EC70D1EA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.2081241996521964E-2"/>
+                  <c:y val="1.7830808077589317E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-0FF1-4E74-A1A5-9B44EC70D1EA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-8.7034177963922002E-3"/>
+                  <c:y val="2.1068369913108429E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-0FF1-4E74-A1A5-9B44EC70D1EA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Logarithmic data'!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1900</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Logarithmic data'!$B$3:$K$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>52.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>256.95</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>357.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>459.75</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>560.6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>660.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>764.95</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>861.3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>952.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-0FF1-4E74-A1A5-9B44EC70D1EA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1128517408"/>
+        <c:axId val="1128517824"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1128517408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Number of folders</a:t>
+                </a:r>
+                <a:endParaRPr lang="el-GR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1128517824"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1128517824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Disks</a:t>
+                </a:r>
+                <a:endParaRPr lang="el-GR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="5.2137643378519288E-3"/>
+              <c:y val="0.43446412083865016"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1128517408"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="el-GR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>Absolut difference in disk usage between algorithms</a:t>
+            </a:r>
+            <a:endParaRPr lang="el-GR"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Logarithmic data'!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1900</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Logarithmic data'!$B$4:$K$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>-6.1999999999999957</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-21.699999999999989</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-36.800000000000011</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-53.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-68.700000000000045</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-85.699999999999932</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-102</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-116.34999999999991</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-134.25</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-152.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5922-4D3C-906F-93F14BB2645B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="769286656"/>
+        <c:axId val="769291648"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="769286656"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Number of folders</a:t>
+                </a:r>
+                <a:endParaRPr lang="el-GR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="769291648"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="769291648"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Difference in disks</a:t>
+                </a:r>
+                <a:endParaRPr lang="el-GR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="769286656"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="el-GR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Precentile</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> difference in disk usage</a:t>
+            </a:r>
+            <a:endParaRPr lang="el-GR"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Logarithmic data'!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1900</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Logarithmic data'!$B$5:$K$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>-11</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-13</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-13</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-13</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-13</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-13</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-13</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-14.000000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8CFD-440A-BF71-36313057CAF0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1956,6 +3694,120 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -2976,6 +4828,1541 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3532,15 +6919,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>23813</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>16124</xdr:rowOff>
+      <xdr:rowOff>28030</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>594360</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>10954</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>154780</xdr:rowOff>
+      <xdr:rowOff>166686</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3588,6 +6975,125 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>601489</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>593869</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Γράφημα 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3383839C-0A50-40C3-9AE1-E7B8B57A57F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>23813</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28030</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>10954</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>166686</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Γράφημα 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C6D35AD-3E91-42CF-ABE8-6C06B2429B14}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>767</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>270717</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>11906</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Γράφημα 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{697A70FF-4AAE-4C3D-9B22-EAFE069AA790}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -3870,7 +7376,7 @@
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="54.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3984,44 +7490,44 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <f>B2-B3</f>
-        <v>6.1999999999999957</v>
+        <f>B3-B2</f>
+        <v>-6.1999999999999957</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:E4" si="0">C2-C3</f>
-        <v>21.699999999999989</v>
+        <f t="shared" ref="C4:K4" si="0">C3-C2</f>
+        <v>-21.699999999999989</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>36.800000000000011</v>
+        <v>-36.800000000000011</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>53.5</v>
+        <v>-53.5</v>
       </c>
       <c r="F4">
-        <f t="shared" ref="F4" si="1">F2-F3</f>
-        <v>68.700000000000045</v>
+        <f t="shared" si="0"/>
+        <v>-68.700000000000045</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4" si="2">G2-G3</f>
-        <v>85.699999999999932</v>
+        <f t="shared" si="0"/>
+        <v>-85.699999999999932</v>
       </c>
       <c r="H4">
-        <f t="shared" ref="H4" si="3">H2-H3</f>
-        <v>102</v>
+        <f t="shared" si="0"/>
+        <v>-102</v>
       </c>
       <c r="I4">
-        <f t="shared" ref="I4" si="4">I2-I3</f>
-        <v>116.34999999999991</v>
+        <f t="shared" si="0"/>
+        <v>-116.34999999999991</v>
       </c>
       <c r="J4">
-        <f t="shared" ref="J4" si="5">J2-J3</f>
-        <v>134.25</v>
+        <f t="shared" si="0"/>
+        <v>-134.25</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4" si="6">K2-K3</f>
-        <v>152.5</v>
+        <f t="shared" si="0"/>
+        <v>-152.5</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -4029,44 +7535,254 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <f>ROUND(B4/B3, 2) * 100</f>
-        <v>12</v>
+        <f>(ROUND(B4/B2, 2) * 100)</f>
+        <v>-11</v>
       </c>
       <c r="C5">
-        <f t="shared" ref="C5:E5" si="7">ROUND(C4/C3, 2) * 100</f>
-        <v>14.000000000000002</v>
+        <f t="shared" ref="C5:K5" si="1">(ROUND(C4/C2, 2) * 100)</f>
+        <v>-12</v>
       </c>
       <c r="D5">
-        <f t="shared" si="7"/>
-        <v>14.000000000000002</v>
+        <f t="shared" si="1"/>
+        <v>-13</v>
       </c>
       <c r="E5">
-        <f t="shared" si="7"/>
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>-13</v>
       </c>
       <c r="F5">
-        <f t="shared" ref="F5" si="8">ROUND(F4/F3, 2) * 100</f>
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>-13</v>
       </c>
       <c r="G5">
-        <f t="shared" ref="G5" si="9">ROUND(G4/G3, 2) * 100</f>
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>-13</v>
       </c>
       <c r="H5">
-        <f t="shared" ref="H5" si="10">ROUND(H4/H3, 2) * 100</f>
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>-13</v>
       </c>
       <c r="I5">
-        <f t="shared" ref="I5" si="11">ROUND(I4/I3, 2) * 100</f>
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>-13</v>
       </c>
       <c r="J5">
-        <f t="shared" ref="J5" si="12">ROUND(J4/J3, 2) * 100</f>
-        <v>16</v>
+        <f t="shared" si="1"/>
+        <v>-13</v>
       </c>
       <c r="K5">
-        <f t="shared" ref="K5" si="13">ROUND(K4/K3, 2) * 100</f>
-        <v>16</v>
+        <f t="shared" si="1"/>
+        <v>-14.000000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8247851E-4746-47B1-81A1-0680B06091CD}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="54.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>100</v>
+      </c>
+      <c r="C1">
+        <v>300</v>
+      </c>
+      <c r="D1">
+        <v>500</v>
+      </c>
+      <c r="E1">
+        <v>700</v>
+      </c>
+      <c r="F1">
+        <v>900</v>
+      </c>
+      <c r="G1">
+        <v>1100</v>
+      </c>
+      <c r="H1">
+        <v>1300</v>
+      </c>
+      <c r="I1">
+        <v>1500</v>
+      </c>
+      <c r="J1">
+        <v>1700</v>
+      </c>
+      <c r="K1">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>58.8</v>
+      </c>
+      <c r="C2">
+        <v>177.7</v>
+      </c>
+      <c r="D2">
+        <v>293.75</v>
+      </c>
+      <c r="E2">
+        <v>411.2</v>
+      </c>
+      <c r="F2">
+        <v>528.45000000000005</v>
+      </c>
+      <c r="G2">
+        <v>646.29999999999995</v>
+      </c>
+      <c r="H2">
+        <v>762.25</v>
+      </c>
+      <c r="I2">
+        <v>881.3</v>
+      </c>
+      <c r="J2">
+        <v>995.55</v>
+      </c>
+      <c r="K2">
+        <v>1105.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>52.6</v>
+      </c>
+      <c r="C3">
+        <v>156</v>
+      </c>
+      <c r="D3">
+        <v>256.95</v>
+      </c>
+      <c r="E3">
+        <v>357.7</v>
+      </c>
+      <c r="F3">
+        <v>459.75</v>
+      </c>
+      <c r="G3">
+        <v>560.6</v>
+      </c>
+      <c r="H3">
+        <v>660.25</v>
+      </c>
+      <c r="I3">
+        <v>764.95</v>
+      </c>
+      <c r="J3">
+        <v>861.3</v>
+      </c>
+      <c r="K3">
+        <v>952.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <f>B3-B2</f>
+        <v>-6.1999999999999957</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:K4" si="0">C3-C2</f>
+        <v>-21.699999999999989</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>-36.800000000000011</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>-53.5</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>-68.700000000000045</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>-85.699999999999932</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>-102</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>-116.34999999999991</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>-134.25</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>-152.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <f>(ROUND(B4/B2, 2) * 100)</f>
+        <v>-11</v>
+      </c>
+      <c r="C5">
+        <f t="shared" ref="C5:K5" si="1">(ROUND(C4/C2, 2) * 100)</f>
+        <v>-12</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>-13</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>-13</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>-13</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>-13</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>-13</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="1"/>
+        <v>-13</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="1"/>
+        <v>-13</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="1"/>
+        <v>-14.000000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/presentation/Παρουσίαση εργασίας 2.xlsx
+++ b/presentation/Παρουσίαση εργασίας 2.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yiann\OneDrive\Υπολογιστής\Σχολείο\ΟΠΑ\Δομές δεδομένων\Εργασία 2\presentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7AEDF6-A4C7-482A-8E3C-8A3C9A1C166D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7478DE4C-0AAA-4B84-8526-36B3FA0A1BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Linear data" sheetId="1" r:id="rId1"/>
-    <sheet name="Logarithmic data" sheetId="2" r:id="rId2"/>
+    <sheet name="linear small data" sheetId="1" r:id="rId1"/>
+    <sheet name="linear big data" sheetId="2" r:id="rId2"/>
+    <sheet name="exponential data" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="6">
   <si>
     <t>Number of Folders</t>
   </si>
@@ -52,6 +53,9 @@
   </si>
   <si>
     <t>Difference from greedy to greedy decreasing algorithm</t>
+  </si>
+  <si>
+    <t>Absolute Precentile difference (Algorithm 2 efficiency increase)</t>
   </si>
 </sst>
 </file>
@@ -201,7 +205,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Linear data'!$A$2</c:f>
+              <c:f>'linear small data'!$A$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -282,78 +286,72 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Linear data'!$B$1:$K$1</c:f>
+              <c:f>'linear small data'!$B$1:$J$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>100</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>300</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>500</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>700</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>900</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1100</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1300</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1500</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>1700</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1900</c:v>
+                  <c:v>800</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Linear data'!$B$2:$K$2</c:f>
+              <c:f>'linear small data'!$B$2:$J$2</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>58.8</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>177.7</c:v>
+                  <c:v>60.7</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>293.75</c:v>
+                  <c:v>117.15</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>411.2</c:v>
+                  <c:v>178.15</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>528.45000000000005</c:v>
+                  <c:v>236.85</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>646.29999999999995</c:v>
+                  <c:v>294.55</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>762.25</c:v>
+                  <c:v>352.2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>881.3</c:v>
+                  <c:v>413.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>995.55</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1105.3</c:v>
+                  <c:v>466.15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -370,7 +368,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Linear data'!$A$3</c:f>
+              <c:f>'linear small data'!$A$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -480,6 +478,116 @@
                 </c:ext>
               </c:extLst>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="4.2025358027885868E-3"/>
+                  <c:y val="1.9891613706509978E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-8AF6-453C-9D4B-3BFB1ED15933}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-6.3551815766164747E-3"/>
+                  <c:y val="2.7840331334262145E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-8AF6-453C-9D4B-3BFB1ED15933}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.5443218120838765E-3"/>
+                  <c:y val="2.7840331334262145E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-8AF6-453C-9D4B-3BFB1ED15933}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-6.355181576616591E-3"/>
+                  <c:y val="2.7840331334262097E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-8AF6-453C-9D4B-3BFB1ED15933}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.4871617519730098E-2"/>
+                  <c:y val="4.1088194047182419E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-8AF6-453C-9D4B-3BFB1ED15933}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -539,78 +647,72 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Linear data'!$B$1:$K$1</c:f>
+              <c:f>'linear small data'!$B$1:$J$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>100</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>300</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>500</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>700</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>900</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1100</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1300</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1500</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>1700</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1900</c:v>
+                  <c:v>800</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Linear data'!$B$3:$K$3</c:f>
+              <c:f>'linear small data'!$B$3:$J$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>52.6</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>156</c:v>
+                  <c:v>54.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>256.95</c:v>
+                  <c:v>103.55</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>357.7</c:v>
+                  <c:v>156.9</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>459.75</c:v>
+                  <c:v>207</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>560.6</c:v>
+                  <c:v>256.64999999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>660.25</c:v>
+                  <c:v>308.45</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>764.95</c:v>
+                  <c:v>361.15</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>861.3</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>952.8</c:v>
+                  <c:v>405.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -937,6 +1039,906 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="el-GR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>Absolut difference in disk usage between algorithms</a:t>
+            </a:r>
+            <a:endParaRPr lang="el-GR"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'exponential data'!$B$1:$J$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'exponential data'!$B$4:$J$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.10000000000000009</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.40000000000000036</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-2.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-5.9500000000000028</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-37.100000000000023</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-77.200000000000045</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-411.44999999999982</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-829.79999999999927</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D41A-423A-8B07-D8BF66CC528C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="769286656"/>
+        <c:axId val="769291648"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="769286656"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Number of folders</a:t>
+                </a:r>
+                <a:endParaRPr lang="el-GR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="769291648"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="769291648"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Difference in disks</a:t>
+                </a:r>
+                <a:endParaRPr lang="el-GR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="769286656"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="el-GR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Absolute p</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>recentile</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> difference in disk usage</a:t>
+            </a:r>
+            <a:endParaRPr lang="el-GR"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'exponential data'!$B$1:$J$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'exponential data'!$B$5:$J$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.7027027027027049</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.4516129032258114</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.2236842105263168</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10.093299406276509</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12.574139976275214</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>13.008678068919039</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14.059696902390261</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14.195777876620921</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5423-4CBA-8FBA-6046B5811292}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1485362208"/>
+        <c:axId val="1485362624"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1485362208"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Number of folders</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1485362624"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1485362624"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>% difference</a:t>
+                </a:r>
+                <a:endParaRPr lang="el-GR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1485362208"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -1029,78 +2031,72 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'Linear data'!$B$1:$K$1</c:f>
+              <c:f>'linear small data'!$B$1:$J$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>100</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>300</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>500</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>700</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>900</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1100</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1300</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1500</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>1700</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1900</c:v>
+                  <c:v>800</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Linear data'!$B$4:$K$4</c:f>
+              <c:f>'linear small data'!$B$4:$J$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>-6.1999999999999957</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-21.699999999999989</c:v>
+                  <c:v>-6.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-36.800000000000011</c:v>
+                  <c:v>-13.600000000000009</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-53.5</c:v>
+                  <c:v>-21.25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-68.700000000000045</c:v>
+                  <c:v>-29.849999999999994</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-85.699999999999932</c:v>
+                  <c:v>-37.900000000000034</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-102</c:v>
+                  <c:v>-43.75</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-116.34999999999991</c:v>
+                  <c:v>-52.450000000000045</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-134.25</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-152.5</c:v>
+                  <c:v>-60.549999999999955</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1423,11 +2419,11 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Precentile</a:t>
+              <a:t>Absolute Precentile difference </a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
-              <a:t> difference in disk usage</a:t>
+              <a:t>in disk usage</a:t>
             </a:r>
             <a:endParaRPr lang="el-GR"/>
           </a:p>
@@ -1485,78 +2481,72 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Linear data'!$B$1:$K$1</c:f>
+              <c:f>'linear small data'!$B$1:$J$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>100</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>300</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>500</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>700</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>900</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1100</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1300</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1500</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>1700</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1900</c:v>
+                  <c:v>800</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Linear data'!$B$5:$K$5</c:f>
+              <c:f>'linear small data'!$B$5:$J$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>-11</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-12</c:v>
+                  <c:v>10.70840197693575</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-13</c:v>
+                  <c:v>11.609048228766545</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-13</c:v>
+                  <c:v>11.928150435026662</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-13</c:v>
+                  <c:v>12.602913236225458</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-13</c:v>
+                  <c:v>12.867085384484819</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-13</c:v>
+                  <c:v>12.421919363997729</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-13</c:v>
+                  <c:v>12.681334622823995</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-13</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-14.000000000000002</c:v>
+                  <c:v>12.989381100504122</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1877,6 +2867,896 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>Absolut difference in disk usage between algorithms</a:t>
+            </a:r>
+            <a:endParaRPr lang="el-GR"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'linear small data'!$B$1:$J$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>800</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'linear small data'!$B$4:$J$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-6.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-13.600000000000009</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-21.25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-29.849999999999994</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-37.900000000000034</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-43.75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-52.450000000000045</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-60.549999999999955</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B616-4436-9109-4408C2D05AB3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="769286656"/>
+        <c:axId val="769291648"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="769286656"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Number of folders</a:t>
+                </a:r>
+                <a:endParaRPr lang="el-GR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="769291648"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="769291648"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Difference in disks</a:t>
+                </a:r>
+                <a:endParaRPr lang="el-GR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="769286656"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="el-GR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>Absolut difference in disk usage between algorithms</a:t>
+            </a:r>
+            <a:endParaRPr lang="el-GR"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'linear small data'!$B$1:$J$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>800</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'linear small data'!$B$4:$J$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-6.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-13.600000000000009</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-21.25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-29.849999999999994</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-37.900000000000034</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-43.75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-52.450000000000045</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-60.549999999999955</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B616-4436-9109-4408C2D05AB3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="769286656"/>
+        <c:axId val="769291648"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="769286656"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Number of folders</a:t>
+                </a:r>
+                <a:endParaRPr lang="el-GR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="769291648"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="769291648"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Difference in disks</a:t>
+                </a:r>
+                <a:endParaRPr lang="el-GR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="769286656"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="el-GR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Disks</a:t>
             </a:r>
@@ -1938,7 +3818,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Logarithmic data'!$A$2</c:f>
+              <c:f>'linear big data'!$A$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2019,78 +3899,54 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Logarithmic data'!$B$1:$K$1</c:f>
+              <c:f>'linear big data'!$B$1:$G$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>300</c:v>
+                  <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>500</c:v>
+                  <c:v>3000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>700</c:v>
+                  <c:v>4000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>900</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1100</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1300</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1500</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1700</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1900</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Logarithmic data'!$B$2:$K$2</c:f>
+              <c:f>'linear big data'!$B$2:$G$2</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>58.8</c:v>
+                  <c:v>583.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>177.7</c:v>
+                  <c:v>1164.9000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>293.75</c:v>
+                  <c:v>1762.4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>411.2</c:v>
+                  <c:v>2340.15</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>528.45000000000005</c:v>
+                  <c:v>2940.75</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>646.29999999999995</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>762.25</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>881.3</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>995.55</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1105.3</c:v>
+                  <c:v>3521.05</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2107,7 +3963,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Logarithmic data'!$A$3</c:f>
+              <c:f>'linear big data'!$A$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2217,6 +4073,50 @@
                 </c:ext>
               </c:extLst>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-9.8901379082137995E-3"/>
+                  <c:y val="2.5981982067278749E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-A40C-4814-BBE2-EC9E40ECB20A}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.9956417656641195E-2"/>
+                  <c:y val="3.4180363091448097E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-A40C-4814-BBE2-EC9E40ECB20A}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -2276,78 +4176,54 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Logarithmic data'!$B$1:$K$1</c:f>
+              <c:f>'linear big data'!$B$1:$G$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>300</c:v>
+                  <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>500</c:v>
+                  <c:v>3000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>700</c:v>
+                  <c:v>4000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>900</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1100</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1300</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1500</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1700</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1900</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Logarithmic data'!$B$3:$K$3</c:f>
+              <c:f>'linear big data'!$B$3:$G$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>52.6</c:v>
+                  <c:v>506.05</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>156</c:v>
+                  <c:v>1004.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>256.95</c:v>
+                  <c:v>1519.85</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>357.7</c:v>
+                  <c:v>2015.6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>459.75</c:v>
+                  <c:v>2532</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>560.6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>660.25</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>764.95</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>861.3</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>952.8</c:v>
+                  <c:v>3027.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2674,7 +4550,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="el-GR"/>
@@ -2766,78 +4642,54 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'Logarithmic data'!$B$1:$K$1</c:f>
+              <c:f>'linear big data'!$B$1:$G$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>300</c:v>
+                  <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>500</c:v>
+                  <c:v>3000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>700</c:v>
+                  <c:v>4000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>900</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1100</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1300</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1500</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1700</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1900</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Logarithmic data'!$B$4:$K$4</c:f>
+              <c:f>'linear big data'!$B$4:$G$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>-6.1999999999999957</c:v>
+                  <c:v>-77.749999999999943</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-21.699999999999989</c:v>
+                  <c:v>-160.60000000000014</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-36.800000000000011</c:v>
+                  <c:v>-242.55000000000018</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-53.5</c:v>
+                  <c:v>-324.55000000000018</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-68.700000000000045</c:v>
+                  <c:v>-408.75</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-85.699999999999932</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-102</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-116.34999999999991</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-134.25</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-152.5</c:v>
+                  <c:v>-493.45000000000027</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3125,7 +4977,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="el-GR"/>
@@ -3159,8 +5011,14 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Absolute p</a:t>
+            </a:r>
+            <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Precentile</a:t>
+              <a:t>recentile</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
@@ -3222,78 +5080,54 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Logarithmic data'!$B$1:$K$1</c:f>
+              <c:f>'linear big data'!$B$1:$G$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>300</c:v>
+                  <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>500</c:v>
+                  <c:v>3000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>700</c:v>
+                  <c:v>4000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>900</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1100</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1300</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1500</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1700</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1900</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Logarithmic data'!$B$5:$K$5</c:f>
+              <c:f>'linear big data'!$B$5:$G$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>-11</c:v>
+                  <c:v>13.317917094895504</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-12</c:v>
+                  <c:v>13.786591123701616</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-13</c:v>
+                  <c:v>13.762482977757612</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-13</c:v>
+                  <c:v>13.868769095998127</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-13</c:v>
+                  <c:v>13.899515429737312</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-13</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-13</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-13</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-13</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-14.000000000000002</c:v>
+                  <c:v>14.014285511424157</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3580,10 +5414,1070 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="el-GR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Disks</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> used by algorithm</a:t>
+            </a:r>
+            <a:endParaRPr lang="el-GR"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.4885529819721436E-2"/>
+          <c:y val="0.11557971014492753"/>
+          <c:w val="0.90425941282887079"/>
+          <c:h val="0.66086161676808042"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'exponential data'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Greedy Algorithm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.9484784687639403E-2"/>
+                  <c:y val="-4.2372698849430096E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000C-3F08-4DD6-A66D-A4C63F446FD6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.10170935921390704"/>
+                  <c:y val="-1.7757316884601554E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000A-3F08-4DD6-A66D-A4C63F446FD6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'exponential data'!$B$1:$J$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'exponential data'!$B$2:$J$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>58.95</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>295.05</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>593.45000000000005</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2926.45</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5845.4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3F08-4DD6-A66D-A4C63F446FD6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'exponential data'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Greedy Decreasing Algorithm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="4.4618217468100365E-4"/>
+                  <c:y val="1.4593246242070085E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-3F08-4DD6-A66D-A4C63F446FD6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.0624460816109467E-2"/>
+                  <c:y val="2.4305912989470203E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-3F08-4DD6-A66D-A4C63F446FD6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.487328364143751E-2"/>
+                  <c:y val="1.7830753850918122E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-3F08-4DD6-A66D-A4C63F446FD6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="5.7571144440618938E-3"/>
+                  <c:y val="2.1068441099030503E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-3F08-4DD6-A66D-A4C63F446FD6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="7.9371917107976704E-3"/>
+                  <c:y val="2.8738404604519225E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-3F08-4DD6-A66D-A4C63F446FD6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="4.7839741042446857E-3"/>
+                  <c:y val="3.1473447045055739E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-3F08-4DD6-A66D-A4C63F446FD6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="3.1772551344475867E-3"/>
+                  <c:y val="6.8580650802271938E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-3F08-4DD6-A66D-A4C63F446FD6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.3464304966899692E-2"/>
+                  <c:y val="1.7798234842373258E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-3F08-4DD6-A66D-A4C63F446FD6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.4496653533320622E-2"/>
+                  <c:y val="6.9764041212567074E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000B-3F08-4DD6-A66D-A4C63F446FD6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'exponential data'!$B$1:$J$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'exponential data'!$B$3:$J$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>257.95</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>516.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2515</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5015.6000000000004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-3F08-4DD6-A66D-A4C63F446FD6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1128517408"/>
+        <c:axId val="1128517824"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1128517408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Number of folders</a:t>
+                </a:r>
+                <a:endParaRPr lang="el-GR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1128517824"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1128517824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Disks</a:t>
+                </a:r>
+                <a:endParaRPr lang="el-GR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="5.2137643378519288E-3"/>
+              <c:y val="0.43446412083865016"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1128517408"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.13020192662051214"/>
+          <c:y val="0.17772951851623733"/>
+          <c:w val="0.22068360958145983"/>
+          <c:h val="9.2308328441124868E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
   <a:schemeClr val="accent2"/>
   <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
   <a:schemeClr val="accent6"/>
   <cs:variation/>
   <cs:variation>
@@ -3769,6 +6663,80 @@
 </file>
 
 <file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3808,6 +6776,43 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -4324,7 +7329,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4827,7 +7832,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5343,8 +8348,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -5452,11 +8457,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -5467,11 +8467,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -5503,9 +8498,6 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5859,8 +8851,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -5968,6 +8960,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -5978,6 +8975,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -6009,6 +9011,9 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6362,8 +9367,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -6471,11 +9476,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -6486,11 +9486,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -6522,6 +9517,2557 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="phClr"/>
       </a:solidFill>
@@ -6882,14 +12428,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>601489</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>587115</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>593869</xdr:colOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>22369</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -6919,13 +12465,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>23813</xdr:colOff>
+      <xdr:colOff>23815</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>28030</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>10954</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>587116</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>166686</xdr:rowOff>
     </xdr:to>
@@ -6988,6 +12534,78 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>11323</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28030</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>574624</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>166686</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Γράφημα 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AA7834E-4BAD-9E55-4A06-2423EC6043FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>40522</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>563301</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>179178</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Γράφημα 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F75ECA6-4804-485B-13F8-2A12E66F1497}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6995,14 +12613,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>601489</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>593869</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>490388</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -7039,8 +12657,8 @@
       <xdr:rowOff>28030</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>10954</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>11906</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>166686</xdr:rowOff>
     </xdr:to>
@@ -7050,6 +12668,125 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C6D35AD-3E91-42CF-ABE8-6C06B2429B14}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>499359</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>167235</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>11906</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Γράφημα 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{697A70FF-4AAE-4C3D-9B22-EAFE069AA790}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>583406</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>593870</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Γράφημα 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E9A8D16-40FF-4617-9937-3D196BA7ACF8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>23813</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28030</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>595312</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>166686</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Γράφημα 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8344A7A8-0123-4EB5-B797-99E4C7987D2F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7087,7 +12824,7 @@
         <xdr:cNvPr id="4" name="Γράφημα 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{697A70FF-4AAE-4C3D-9B22-EAFE069AA790}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6020D7D3-6852-4D45-AB1B-FF1ED0AF27F2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7373,206 +13110,189 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="54.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
         <v>100</v>
       </c>
-      <c r="C1">
+      <c r="D1">
+        <v>200</v>
+      </c>
+      <c r="E1">
         <v>300</v>
       </c>
-      <c r="D1">
+      <c r="F1">
+        <v>400</v>
+      </c>
+      <c r="G1">
         <v>500</v>
       </c>
-      <c r="E1">
+      <c r="H1">
+        <v>600</v>
+      </c>
+      <c r="I1">
         <v>700</v>
       </c>
-      <c r="F1">
-        <v>900</v>
-      </c>
-      <c r="G1">
-        <v>1100</v>
-      </c>
-      <c r="H1">
-        <v>1300</v>
-      </c>
-      <c r="I1">
-        <v>1500</v>
-      </c>
       <c r="J1">
-        <v>1700</v>
-      </c>
-      <c r="K1">
-        <v>1900</v>
+        <v>800</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
-        <v>58.8</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>177.7</v>
+        <v>60.7</v>
       </c>
       <c r="D2">
-        <v>293.75</v>
+        <v>117.15</v>
       </c>
       <c r="E2">
-        <v>411.2</v>
+        <v>178.15</v>
       </c>
       <c r="F2">
-        <v>528.45000000000005</v>
+        <v>236.85</v>
       </c>
       <c r="G2">
-        <v>646.29999999999995</v>
+        <v>294.55</v>
       </c>
       <c r="H2">
-        <v>762.25</v>
+        <v>352.2</v>
       </c>
       <c r="I2">
-        <v>881.3</v>
+        <v>413.6</v>
       </c>
       <c r="J2">
-        <v>995.55</v>
-      </c>
-      <c r="K2">
-        <v>1105.3</v>
+        <v>466.15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>52.6</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>156</v>
+        <v>54.2</v>
       </c>
       <c r="D3">
-        <v>256.95</v>
+        <v>103.55</v>
       </c>
       <c r="E3">
-        <v>357.7</v>
+        <v>156.9</v>
       </c>
       <c r="F3">
-        <v>459.75</v>
+        <v>207</v>
       </c>
       <c r="G3">
-        <v>560.6</v>
+        <v>256.64999999999998</v>
       </c>
       <c r="H3">
-        <v>660.25</v>
+        <v>308.45</v>
       </c>
       <c r="I3">
-        <v>764.95</v>
+        <v>361.15</v>
       </c>
       <c r="J3">
-        <v>861.3</v>
-      </c>
-      <c r="K3">
-        <v>952.8</v>
+        <v>405.6</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4">
         <f>B3-B2</f>
-        <v>-6.1999999999999957</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <f t="shared" ref="C4:K4" si="0">C3-C2</f>
-        <v>-21.699999999999989</v>
+        <v>-6.5</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>-36.800000000000011</v>
+        <v>-13.600000000000009</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>-53.5</v>
+        <v>-21.25</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>-68.700000000000045</v>
+        <v>-29.849999999999994</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>-85.699999999999932</v>
+        <v>-37.900000000000034</v>
       </c>
       <c r="H4">
         <f t="shared" si="0"/>
-        <v>-102</v>
+        <v>-43.75</v>
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>-116.34999999999991</v>
+        <v>-52.450000000000045</v>
       </c>
       <c r="J4">
         <f t="shared" si="0"/>
-        <v>-134.25</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="0"/>
-        <v>-152.5</v>
+        <v>-60.549999999999955</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <f>(ROUND(B4/B2, 2) * 100)</f>
-        <v>-11</v>
+        <f>ABS(B4/B2*100)</f>
+        <v>0</v>
       </c>
       <c r="C5">
-        <f t="shared" ref="C5:K5" si="1">(ROUND(C4/C2, 2) * 100)</f>
-        <v>-12</v>
+        <f t="shared" ref="C5:J5" si="1">ABS(C4/C2*100)</f>
+        <v>10.70840197693575</v>
       </c>
       <c r="D5">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>11.609048228766545</v>
       </c>
       <c r="E5">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>11.928150435026662</v>
       </c>
       <c r="F5">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>12.602913236225458</v>
       </c>
       <c r="G5">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>12.867085384484819</v>
       </c>
       <c r="H5">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>12.421919363997729</v>
       </c>
       <c r="I5">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>12.681334622823995</v>
       </c>
       <c r="J5">
         <f t="shared" si="1"/>
-        <v>-13</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="1"/>
-        <v>-14.000000000000002</v>
+        <v>12.989381100504122</v>
       </c>
     </row>
   </sheetData>
@@ -7583,206 +13303,332 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8247851E-4746-47B1-81A1-0680B06091CD}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="54.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>1000</v>
+      </c>
+      <c r="C1">
+        <v>2000</v>
+      </c>
+      <c r="D1">
+        <v>3000</v>
+      </c>
+      <c r="E1">
+        <v>4000</v>
+      </c>
+      <c r="F1">
+        <v>5000</v>
+      </c>
+      <c r="G1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>583.79999999999995</v>
+      </c>
+      <c r="C2">
+        <v>1164.9000000000001</v>
+      </c>
+      <c r="D2">
+        <v>1762.4</v>
+      </c>
+      <c r="E2">
+        <v>2340.15</v>
+      </c>
+      <c r="F2">
+        <v>2940.75</v>
+      </c>
+      <c r="G2">
+        <v>3521.05</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>506.05</v>
+      </c>
+      <c r="C3">
+        <v>1004.3</v>
+      </c>
+      <c r="D3">
+        <v>1519.85</v>
+      </c>
+      <c r="E3">
+        <v>2015.6</v>
+      </c>
+      <c r="F3">
+        <v>2532</v>
+      </c>
+      <c r="G3">
+        <v>3027.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <f>B3-B2</f>
+        <v>-77.749999999999943</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:K4" si="0">C3-C2</f>
+        <v>-160.60000000000014</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>-242.55000000000018</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>-324.55000000000018</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>-408.75</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>-493.45000000000027</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <f>ABS(B4/B2*100)</f>
+        <v>13.317917094895504</v>
+      </c>
+      <c r="C5">
+        <f t="shared" ref="C5:G5" si="1">ABS(C4/C2*100)</f>
+        <v>13.786591123701616</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>13.762482977757612</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>13.868769095998127</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>13.899515429737312</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>14.014285511424157</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F267604B-1025-4E1E-8780-70DB95202005}">
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="54.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>5</v>
+      </c>
+      <c r="D1">
+        <v>10</v>
+      </c>
+      <c r="E1">
+        <v>50</v>
+      </c>
+      <c r="F1">
         <v>100</v>
       </c>
-      <c r="C1">
-        <v>300</v>
-      </c>
-      <c r="D1">
+      <c r="G1">
         <v>500</v>
       </c>
-      <c r="E1">
-        <v>700</v>
-      </c>
-      <c r="F1">
-        <v>900</v>
-      </c>
-      <c r="G1">
-        <v>1100</v>
-      </c>
       <c r="H1">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="I1">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="J1">
-        <v>1700</v>
-      </c>
-      <c r="K1">
-        <v>1900</v>
+        <v>10000</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
-        <v>58.8</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>177.7</v>
+        <v>3.7</v>
       </c>
       <c r="D2">
-        <v>293.75</v>
+        <v>6.2</v>
       </c>
       <c r="E2">
-        <v>411.2</v>
+        <v>30.4</v>
       </c>
       <c r="F2">
-        <v>528.45000000000005</v>
+        <v>58.95</v>
       </c>
       <c r="G2">
-        <v>646.29999999999995</v>
+        <v>295.05</v>
       </c>
       <c r="H2">
-        <v>762.25</v>
+        <v>593.45000000000005</v>
       </c>
       <c r="I2">
-        <v>881.3</v>
+        <v>2926.45</v>
       </c>
       <c r="J2">
-        <v>995.55</v>
-      </c>
-      <c r="K2">
-        <v>1105.3</v>
+        <v>5845.4</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>52.6</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>156</v>
+        <v>3.6</v>
       </c>
       <c r="D3">
-        <v>256.95</v>
+        <v>5.8</v>
       </c>
       <c r="E3">
-        <v>357.7</v>
+        <v>27.9</v>
       </c>
       <c r="F3">
-        <v>459.75</v>
+        <v>53</v>
       </c>
       <c r="G3">
-        <v>560.6</v>
+        <v>257.95</v>
       </c>
       <c r="H3">
-        <v>660.25</v>
+        <v>516.25</v>
       </c>
       <c r="I3">
-        <v>764.95</v>
+        <v>2515</v>
       </c>
       <c r="J3">
-        <v>861.3</v>
-      </c>
-      <c r="K3">
-        <v>952.8</v>
+        <v>5015.6000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4">
         <f>B3-B2</f>
-        <v>-6.1999999999999957</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <f t="shared" ref="C4:K4" si="0">C3-C2</f>
-        <v>-21.699999999999989</v>
+        <v>-0.10000000000000009</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>-36.800000000000011</v>
+        <v>-0.40000000000000036</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>-53.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>-68.700000000000045</v>
+        <v>-5.9500000000000028</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>-85.699999999999932</v>
+        <v>-37.100000000000023</v>
       </c>
       <c r="H4">
         <f t="shared" si="0"/>
-        <v>-102</v>
+        <v>-77.200000000000045</v>
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>-116.34999999999991</v>
+        <v>-411.44999999999982</v>
       </c>
       <c r="J4">
         <f t="shared" si="0"/>
-        <v>-134.25</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="0"/>
-        <v>-152.5</v>
+        <v>-829.79999999999927</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5">
-        <f>(ROUND(B4/B2, 2) * 100)</f>
-        <v>-11</v>
+        <f>ABS(B4/B2*100)</f>
+        <v>0</v>
       </c>
       <c r="C5">
-        <f t="shared" ref="C5:K5" si="1">(ROUND(C4/C2, 2) * 100)</f>
-        <v>-12</v>
+        <f t="shared" ref="C5:J5" si="1">ABS(C4/C2*100)</f>
+        <v>2.7027027027027049</v>
       </c>
       <c r="D5">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>6.4516129032258114</v>
       </c>
       <c r="E5">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>8.2236842105263168</v>
       </c>
       <c r="F5">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>10.093299406276509</v>
       </c>
       <c r="G5">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>12.574139976275214</v>
       </c>
       <c r="H5">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>13.008678068919039</v>
       </c>
       <c r="I5">
         <f t="shared" si="1"/>
-        <v>-13</v>
+        <v>14.059696902390261</v>
       </c>
       <c r="J5">
         <f t="shared" si="1"/>
-        <v>-13</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="1"/>
-        <v>-14.000000000000002</v>
+        <v>14.195777876620921</v>
       </c>
     </row>
   </sheetData>

--- a/presentation/Παρουσίαση εργασίας 2.xlsx
+++ b/presentation/Παρουσίαση εργασίας 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yiann\OneDrive\Υπολογιστής\Σχολείο\ΟΠΑ\Δομές δεδομένων\Εργασία 2\presentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7478DE4C-0AAA-4B84-8526-36B3FA0A1BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABB53E0-E357-43C5-8F40-7F9747250868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="12" windowWidth="23016" windowHeight="12228" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="linear small data" sheetId="1" r:id="rId1"/>
@@ -13222,7 +13222,7 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:K4" si="0">C3-C2</f>
+        <f t="shared" ref="C4:J4" si="0">C3-C2</f>
         <v>-6.5</v>
       </c>
       <c r="D4">
@@ -13389,7 +13389,7 @@
         <v>-77.749999999999943</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:K4" si="0">C3-C2</f>
+        <f t="shared" ref="C4:G4" si="0">C3-C2</f>
         <v>-160.60000000000014</v>
       </c>
       <c r="D4">
@@ -13558,7 +13558,7 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:K4" si="0">C3-C2</f>
+        <f t="shared" ref="C4:J4" si="0">C3-C2</f>
         <v>-0.10000000000000009</v>
       </c>
       <c r="D4">

--- a/presentation/Παρουσίαση εργασίας 2.xlsx
+++ b/presentation/Παρουσίαση εργασίας 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yiann\OneDrive\Υπολογιστής\Σχολείο\ΟΠΑ\Δομές δεδομένων\Εργασία 2\presentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABB53E0-E357-43C5-8F40-7F9747250868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5340D1-682D-4758-B86F-93B648E19F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="12" windowWidth="23016" windowHeight="12228" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="12" windowWidth="23016" windowHeight="12228" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="linear small data" sheetId="1" r:id="rId1"/>
@@ -1129,6 +1129,79 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="movingAvg"/>
+            <c:period val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:numRef>
               <c:f>'exponential data'!$B$1:$J$1</c:f>
@@ -1208,8 +1281,9 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -1439,6 +1513,45 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:dTable>
+        <c:showHorzBorder val="1"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+      </c:dTable>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -3368,6 +3481,78 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:numRef>
               <c:f>'linear small data'!$B$1:$J$1</c:f>
@@ -3447,8 +3632,9 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -3678,6 +3864,45 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:dTable>
+        <c:showHorzBorder val="1"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+      </c:dTable>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -4640,6 +4865,78 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:numRef>
               <c:f>'linear big data'!$B$1:$G$1</c:f>
@@ -4701,8 +4998,9 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -4932,6 +5230,45 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:dTable>
+        <c:showHorzBorder val="1"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+      </c:dTable>
       <c:spPr>
         <a:noFill/>
         <a:ln>
